--- a/artfynd/A 45320-2024 artfynd.xlsx
+++ b/artfynd/A 45320-2024 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121150408</v>
+        <v>121150405</v>
       </c>
       <c r="B9" t="n">
-        <v>89743</v>
+        <v>78337</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767664</v>
+        <v>767770</v>
       </c>
       <c r="R9" t="n">
-        <v>7302951</v>
+        <v>7302809</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121150410</v>
+        <v>121150412</v>
       </c>
       <c r="B10" t="n">
-        <v>79187</v>
+        <v>91985</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767566</v>
+        <v>767515</v>
       </c>
       <c r="R10" t="n">
-        <v>7302978</v>
+        <v>7302930</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1611,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121150411</v>
+        <v>121150410</v>
       </c>
       <c r="B11" t="n">
-        <v>91963</v>
+        <v>79190</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,25 +1623,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767522</v>
+        <v>767566</v>
       </c>
       <c r="R11" t="n">
-        <v>7303001</v>
+        <v>7302978</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1722,10 +1722,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121150407</v>
+        <v>121150408</v>
       </c>
       <c r="B12" t="n">
-        <v>78243</v>
+        <v>89753</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1738,21 +1738,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767719</v>
+        <v>767664</v>
       </c>
       <c r="R12" t="n">
-        <v>7302949</v>
+        <v>7302951</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121150406</v>
+        <v>121150409</v>
       </c>
       <c r="B13" t="n">
-        <v>91975</v>
+        <v>78337</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1845,25 +1845,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>767736</v>
+        <v>767604</v>
       </c>
       <c r="R13" t="n">
-        <v>7302858</v>
+        <v>7302977</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121150405</v>
+        <v>121150411</v>
       </c>
       <c r="B14" t="n">
-        <v>78334</v>
+        <v>91973</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1956,25 +1956,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>767770</v>
+        <v>767522</v>
       </c>
       <c r="R14" t="n">
-        <v>7302809</v>
+        <v>7303001</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121150412</v>
+        <v>121150404</v>
       </c>
       <c r="B15" t="n">
-        <v>91975</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,25 +2067,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>767515</v>
+        <v>767915</v>
       </c>
       <c r="R15" t="n">
-        <v>7302930</v>
+        <v>7302797</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121150409</v>
+        <v>121150406</v>
       </c>
       <c r="B16" t="n">
-        <v>78334</v>
+        <v>91985</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2178,25 +2178,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>767604</v>
+        <v>767736</v>
       </c>
       <c r="R16" t="n">
-        <v>7302977</v>
+        <v>7302858</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121150404</v>
+        <v>121150407</v>
       </c>
       <c r="B17" t="n">
-        <v>78598</v>
+        <v>78246</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2293,21 +2293,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>767915</v>
+        <v>767719</v>
       </c>
       <c r="R17" t="n">
-        <v>7302797</v>
+        <v>7302949</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 45320-2024 artfynd.xlsx
+++ b/artfynd/A 45320-2024 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121150405</v>
+        <v>121150407</v>
       </c>
       <c r="B9" t="n">
-        <v>78337</v>
+        <v>78246</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767770</v>
+        <v>767719</v>
       </c>
       <c r="R9" t="n">
-        <v>7302809</v>
+        <v>7302949</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121150412</v>
+        <v>121150405</v>
       </c>
       <c r="B10" t="n">
-        <v>91985</v>
+        <v>78337</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767515</v>
+        <v>767770</v>
       </c>
       <c r="R10" t="n">
-        <v>7302930</v>
+        <v>7302809</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1611,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121150410</v>
+        <v>121150404</v>
       </c>
       <c r="B11" t="n">
-        <v>79190</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1627,21 +1627,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767566</v>
+        <v>767915</v>
       </c>
       <c r="R11" t="n">
-        <v>7302978</v>
+        <v>7302797</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1722,10 +1722,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121150408</v>
+        <v>121150409</v>
       </c>
       <c r="B12" t="n">
-        <v>89753</v>
+        <v>78337</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1738,21 +1738,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767664</v>
+        <v>767604</v>
       </c>
       <c r="R12" t="n">
-        <v>7302951</v>
+        <v>7302977</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121150409</v>
+        <v>121150408</v>
       </c>
       <c r="B13" t="n">
-        <v>78337</v>
+        <v>89753</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1849,21 +1849,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>767604</v>
+        <v>767664</v>
       </c>
       <c r="R13" t="n">
-        <v>7302977</v>
+        <v>7302951</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121150411</v>
+        <v>121150412</v>
       </c>
       <c r="B14" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>767522</v>
+        <v>767515</v>
       </c>
       <c r="R14" t="n">
-        <v>7303001</v>
+        <v>7302930</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2018,12 +2018,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2055,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121150404</v>
+        <v>121150410</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>79190</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>767915</v>
+        <v>767566</v>
       </c>
       <c r="R15" t="n">
-        <v>7302797</v>
+        <v>7302978</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121150407</v>
+        <v>121150411</v>
       </c>
       <c r="B17" t="n">
-        <v>78246</v>
+        <v>91973</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,25 +2289,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>767719</v>
+        <v>767522</v>
       </c>
       <c r="R17" t="n">
-        <v>7302949</v>
+        <v>7303001</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 45320-2024 artfynd.xlsx
+++ b/artfynd/A 45320-2024 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121150407</v>
+        <v>121150409</v>
       </c>
       <c r="B9" t="n">
-        <v>78246</v>
+        <v>78340</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767719</v>
+        <v>767604</v>
       </c>
       <c r="R9" t="n">
-        <v>7302949</v>
+        <v>7302977</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121150405</v>
+        <v>121150410</v>
       </c>
       <c r="B10" t="n">
-        <v>78337</v>
+        <v>79193</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767770</v>
+        <v>767566</v>
       </c>
       <c r="R10" t="n">
-        <v>7302809</v>
+        <v>7302978</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121150404</v>
+        <v>121150411</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>91985</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,25 +1623,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767915</v>
+        <v>767522</v>
       </c>
       <c r="R11" t="n">
-        <v>7302797</v>
+        <v>7303001</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1722,10 +1722,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121150409</v>
+        <v>121150405</v>
       </c>
       <c r="B12" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767604</v>
+        <v>767770</v>
       </c>
       <c r="R12" t="n">
-        <v>7302977</v>
+        <v>7302809</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121150408</v>
+        <v>121150412</v>
       </c>
       <c r="B13" t="n">
-        <v>89753</v>
+        <v>91997</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1845,25 +1845,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>767664</v>
+        <v>767515</v>
       </c>
       <c r="R13" t="n">
-        <v>7302951</v>
+        <v>7302930</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121150412</v>
+        <v>121150404</v>
       </c>
       <c r="B14" t="n">
-        <v>91985</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1956,25 +1956,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>767515</v>
+        <v>767915</v>
       </c>
       <c r="R14" t="n">
-        <v>7302930</v>
+        <v>7302797</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2018,12 +2018,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2055,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121150410</v>
+        <v>121150407</v>
       </c>
       <c r="B15" t="n">
-        <v>79190</v>
+        <v>78249</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>767566</v>
+        <v>767719</v>
       </c>
       <c r="R15" t="n">
-        <v>7302978</v>
+        <v>7302949</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2169,7 +2169,7 @@
         <v>121150406</v>
       </c>
       <c r="B16" t="n">
-        <v>91985</v>
+        <v>91997</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121150411</v>
+        <v>121150408</v>
       </c>
       <c r="B17" t="n">
-        <v>91973</v>
+        <v>89760</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,25 +2289,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>767522</v>
+        <v>767664</v>
       </c>
       <c r="R17" t="n">
-        <v>7303001</v>
+        <v>7302951</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 45320-2024 artfynd.xlsx
+++ b/artfynd/A 45320-2024 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121150409</v>
+        <v>121150406</v>
       </c>
       <c r="B9" t="n">
-        <v>78340</v>
+        <v>91998</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767604</v>
+        <v>767736</v>
       </c>
       <c r="R9" t="n">
-        <v>7302977</v>
+        <v>7302858</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121150410</v>
+        <v>121150408</v>
       </c>
       <c r="B10" t="n">
-        <v>79193</v>
+        <v>89761</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767566</v>
+        <v>767664</v>
       </c>
       <c r="R10" t="n">
-        <v>7302978</v>
+        <v>7302951</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121150411</v>
+        <v>121150407</v>
       </c>
       <c r="B11" t="n">
-        <v>91985</v>
+        <v>78249</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,25 +1623,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767522</v>
+        <v>767719</v>
       </c>
       <c r="R11" t="n">
-        <v>7303001</v>
+        <v>7302949</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121150405</v>
+        <v>121150409</v>
       </c>
       <c r="B12" t="n">
         <v>78340</v>
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767770</v>
+        <v>767604</v>
       </c>
       <c r="R12" t="n">
-        <v>7302809</v>
+        <v>7302977</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1836,7 +1836,7 @@
         <v>121150412</v>
       </c>
       <c r="B13" t="n">
-        <v>91997</v>
+        <v>91998</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121150407</v>
+        <v>121150411</v>
       </c>
       <c r="B15" t="n">
-        <v>78249</v>
+        <v>91986</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,25 +2067,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>767719</v>
+        <v>767522</v>
       </c>
       <c r="R15" t="n">
-        <v>7302949</v>
+        <v>7303001</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121150406</v>
+        <v>121150405</v>
       </c>
       <c r="B16" t="n">
-        <v>91997</v>
+        <v>78340</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2178,25 +2178,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>767736</v>
+        <v>767770</v>
       </c>
       <c r="R16" t="n">
-        <v>7302858</v>
+        <v>7302809</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121150408</v>
+        <v>121150410</v>
       </c>
       <c r="B17" t="n">
-        <v>89760</v>
+        <v>79193</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2293,21 +2293,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>767664</v>
+        <v>767566</v>
       </c>
       <c r="R17" t="n">
-        <v>7302951</v>
+        <v>7302978</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 45320-2024 artfynd.xlsx
+++ b/artfynd/A 45320-2024 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121150406</v>
+        <v>121150407</v>
       </c>
       <c r="B9" t="n">
-        <v>91998</v>
+        <v>78252</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767736</v>
+        <v>767719</v>
       </c>
       <c r="R9" t="n">
-        <v>7302858</v>
+        <v>7302949</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121150408</v>
+        <v>121150406</v>
       </c>
       <c r="B10" t="n">
-        <v>89761</v>
+        <v>92001</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767664</v>
+        <v>767736</v>
       </c>
       <c r="R10" t="n">
-        <v>7302951</v>
+        <v>7302858</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121150407</v>
+        <v>121150404</v>
       </c>
       <c r="B11" t="n">
-        <v>78249</v>
+        <v>78607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1627,21 +1627,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767719</v>
+        <v>767915</v>
       </c>
       <c r="R11" t="n">
-        <v>7302949</v>
+        <v>7302797</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1722,10 +1722,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121150409</v>
+        <v>121150408</v>
       </c>
       <c r="B12" t="n">
-        <v>78340</v>
+        <v>89764</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1738,21 +1738,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767604</v>
+        <v>767664</v>
       </c>
       <c r="R12" t="n">
-        <v>7302977</v>
+        <v>7302951</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1836,7 +1836,7 @@
         <v>121150412</v>
       </c>
       <c r="B13" t="n">
-        <v>91998</v>
+        <v>92001</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121150404</v>
+        <v>121150410</v>
       </c>
       <c r="B14" t="n">
-        <v>78604</v>
+        <v>79196</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>767915</v>
+        <v>767566</v>
       </c>
       <c r="R14" t="n">
-        <v>7302797</v>
+        <v>7302978</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121150411</v>
+        <v>121150409</v>
       </c>
       <c r="B15" t="n">
-        <v>91986</v>
+        <v>78343</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,25 +2067,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>767522</v>
+        <v>767604</v>
       </c>
       <c r="R15" t="n">
-        <v>7303001</v>
+        <v>7302977</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121150405</v>
+        <v>121150411</v>
       </c>
       <c r="B16" t="n">
-        <v>78340</v>
+        <v>91989</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2178,25 +2178,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>767770</v>
+        <v>767522</v>
       </c>
       <c r="R16" t="n">
-        <v>7302809</v>
+        <v>7303001</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121150410</v>
+        <v>121150405</v>
       </c>
       <c r="B17" t="n">
-        <v>79193</v>
+        <v>78343</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2293,21 +2293,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>767566</v>
+        <v>767770</v>
       </c>
       <c r="R17" t="n">
-        <v>7302978</v>
+        <v>7302809</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 45320-2024 artfynd.xlsx
+++ b/artfynd/A 45320-2024 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121150407</v>
+        <v>121150411</v>
       </c>
       <c r="B9" t="n">
-        <v>78252</v>
+        <v>91989</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767719</v>
+        <v>767522</v>
       </c>
       <c r="R9" t="n">
-        <v>7302949</v>
+        <v>7303001</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121150406</v>
+        <v>121150409</v>
       </c>
       <c r="B10" t="n">
-        <v>92001</v>
+        <v>78343</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767736</v>
+        <v>767604</v>
       </c>
       <c r="R10" t="n">
-        <v>7302858</v>
+        <v>7302977</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121150404</v>
+        <v>121150410</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
+        <v>79196</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1627,21 +1627,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767915</v>
+        <v>767566</v>
       </c>
       <c r="R11" t="n">
-        <v>7302797</v>
+        <v>7302978</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1722,10 +1722,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121150408</v>
+        <v>121150406</v>
       </c>
       <c r="B12" t="n">
-        <v>89764</v>
+        <v>92001</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1734,25 +1734,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767664</v>
+        <v>767736</v>
       </c>
       <c r="R12" t="n">
-        <v>7302951</v>
+        <v>7302858</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121150410</v>
+        <v>121150407</v>
       </c>
       <c r="B14" t="n">
-        <v>79196</v>
+        <v>78252</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>767566</v>
+        <v>767719</v>
       </c>
       <c r="R14" t="n">
-        <v>7302978</v>
+        <v>7302949</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121150409</v>
+        <v>121150408</v>
       </c>
       <c r="B15" t="n">
-        <v>78343</v>
+        <v>89764</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>767604</v>
+        <v>767664</v>
       </c>
       <c r="R15" t="n">
-        <v>7302977</v>
+        <v>7302951</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121150411</v>
+        <v>121150404</v>
       </c>
       <c r="B16" t="n">
-        <v>91989</v>
+        <v>78607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2178,25 +2178,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>767522</v>
+        <v>767915</v>
       </c>
       <c r="R16" t="n">
-        <v>7303001</v>
+        <v>7302797</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
